--- a/education_forms/039_open_source_education_initiative_registration--education_forms.xlsx
+++ b/education_forms/039_open_source_education_initiative_registration--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>program_type</t>
+          <t>program_type_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>program_description</t>
+          <t>program_description_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Program Description</t>
+          <t>Program Description 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Contact Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>program_url</t>
+          <t>program_url_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Program URL</t>
+          <t>Program Url 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>program_url</t>
+          <t>program_url_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Program URL</t>
+          <t>Program Url 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1165,7 +1165,7 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1377,7 +1377,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>program_type_choices</t>
+          <t>program_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1394,7 +1394,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>program_type_choices</t>
+          <t>program_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>program_type_choices</t>
+          <t>program_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
